--- a/Melgar_Ex3A_tables.xlsx
+++ b/Melgar_Ex3A_tables.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\demymelgar\Documents\DATA_Labs\W2_Workshop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46611D97-C035-4229-929D-EE0308570715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BDFBA83-98E1-43B4-8026-2BBEBF763246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4728" yWindow="0" windowWidth="18420" windowHeight="13776" xr2:uid="{84E36D67-CE5C-4529-9BD8-1BF7B43E1293}"/>
+    <workbookView xWindow="4716" yWindow="2352" windowWidth="18420" windowHeight="12516" activeTab="2" xr2:uid="{84E36D67-CE5C-4529-9BD8-1BF7B43E1293}"/>
   </bookViews>
   <sheets>
-    <sheet name="LANA_DATA_SHEET" sheetId="6" r:id="rId1"/>
-    <sheet name="CLIENTS" sheetId="7" r:id="rId2"/>
-    <sheet name="DOGS" sheetId="1" r:id="rId3"/>
-    <sheet name="WALKS" sheetId="2" r:id="rId4"/>
-    <sheet name="EMPLOYEES" sheetId="3" r:id="rId5"/>
-    <sheet name="PAYMENTS" sheetId="5" r:id="rId6"/>
+    <sheet name="lana_dog_walking" sheetId="6" r:id="rId1"/>
+    <sheet name="Clients" sheetId="7" r:id="rId2"/>
+    <sheet name="Dogs" sheetId="1" r:id="rId3"/>
+    <sheet name="Walks" sheetId="2" r:id="rId4"/>
+    <sheet name="Employees" sheetId="3" r:id="rId5"/>
+    <sheet name="Payments" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -392,22 +392,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -1260,7 +1255,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>75</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -1269,147 +1264,147 @@
       <c r="C1" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="5">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="5">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="3" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="5">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="3" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="5">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="3" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="5">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="3" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="5">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="3" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="5">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="3" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="5">
+      <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="5">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="3" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="5">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="3" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1430,7 +1425,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>75</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -1439,279 +1434,279 @@
       <c r="C1" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="8">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="3">
         <v>1</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="3">
         <v>1</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="4">
         <v>45734</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="8">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="3">
         <v>2</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="3">
         <v>3</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="4">
         <v>44938</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="8">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="3">
         <v>3</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="3">
         <v>2</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="4">
         <v>45326</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="8">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="3">
         <v>4</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="3">
         <v>2</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="4">
         <v>45637</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="8">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="3">
         <v>5</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="3">
         <v>1</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="4">
         <v>45749</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="8">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="3">
         <v>6</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="3">
         <v>4</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="4">
         <v>44875</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="8">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="3">
         <v>7</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="3">
         <v>3</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="4">
         <v>45097</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="8">
+      <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="3">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="3">
         <v>2</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="4">
         <v>45550</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="8">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="3">
         <v>9</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="3">
         <v>2</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="4">
         <v>45523</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="8">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="3">
         <v>10</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="3">
         <v>5</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="4">
         <v>44302</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="3" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1731,21 +1726,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="9" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="14">
+      <c r="B2" s="3">
         <v>1</v>
       </c>
       <c r="C2" s="1">
@@ -1753,10 +1748,10 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="3">
         <v>2</v>
       </c>
       <c r="C3" s="1">
@@ -1764,10 +1759,10 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="3">
         <v>3</v>
       </c>
       <c r="C4" s="1">
@@ -1775,10 +1770,10 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="3">
         <v>4</v>
       </c>
       <c r="C5" s="1">
@@ -1786,10 +1781,10 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="3">
         <v>5</v>
       </c>
       <c r="C6" s="1">
@@ -1797,10 +1792,10 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="3">
         <v>6</v>
       </c>
       <c r="C7" s="1">
@@ -1808,10 +1803,10 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="3">
         <v>7</v>
       </c>
       <c r="C8" s="1">
@@ -1819,10 +1814,10 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="3">
         <v>8</v>
       </c>
       <c r="C9" s="1">
@@ -1830,10 +1825,10 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="3">
         <v>9</v>
       </c>
       <c r="C10" s="1">
@@ -1841,10 +1836,10 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="3">
         <v>10</v>
       </c>
       <c r="C11" s="1">
@@ -1867,156 +1862,156 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="7" t="s">
         <v>81</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="10">
+      <c r="B2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="3">
         <v>1</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="3" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="10">
+      <c r="B3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="3">
         <v>2</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="3">
         <v>3</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="3" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="10">
+      <c r="B5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="3">
         <v>4</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="3">
         <v>5</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="10">
+      <c r="B7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="3">
         <v>6</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="3">
         <v>7</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="10">
+      <c r="B9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="3">
         <v>8</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="3" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="10">
+      <c r="B10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="3">
         <v>9</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="3" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="10">
+      <c r="B11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="3">
         <v>10</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="3" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2038,7 +2033,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="8" t="s">
         <v>82</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -2050,210 +2045,210 @@
       <c r="D1" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="14">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="3">
         <v>1</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="14">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="3">
         <v>2</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="14">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="3">
         <v>3</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="14">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="3">
         <v>4</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="14">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="3">
         <v>5</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="3" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="14">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="3">
         <v>6</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="3" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="14">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="3">
         <v>7</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="3" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="14">
+      <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="3">
         <v>8</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="3" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="14">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="3">
         <v>9</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="F10" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="14">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="3">
         <v>10</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="3" t="s">
         <v>22</v>
       </c>
     </row>
